--- a/Config/Luban/source/TbRoomMode.xlsx
+++ b/Config/Luban/source/TbRoomMode.xlsx
@@ -386,7 +386,7 @@
       </c>
       <c r="F1" s="6" t="inlineStr">
         <is>
-          <t>arenaId</t>
+          <t>mapId</t>
         </is>
       </c>
       <c r="G1" s="6" t="inlineStr">
@@ -520,7 +520,7 @@
       </c>
       <c r="F3" s="9" t="inlineStr">
         <is>
-          <t>场地 ID</t>
+          <t>地图 ID</t>
         </is>
       </c>
       <c r="G3" s="9" t="inlineStr">

--- a/Config/Luban/source/TbRoomMode.xlsx
+++ b/Config/Luban/source/TbRoomMode.xlsx
@@ -340,7 +340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="1" min="1" max="1"/>
@@ -376,50 +376,45 @@
       </c>
       <c r="D1" s="6" t="inlineStr">
         <is>
-          <t>characterId</t>
+          <t>heroId</t>
         </is>
       </c>
       <c r="E1" s="6" t="inlineStr">
         <is>
-          <t>weaponId</t>
+          <t>mapId</t>
         </is>
       </c>
       <c r="F1" s="6" t="inlineStr">
         <is>
-          <t>mapId</t>
+          <t>maxPlayers</t>
         </is>
       </c>
       <c r="G1" s="6" t="inlineStr">
         <is>
-          <t>maxPlayers</t>
+          <t>minPlayers</t>
         </is>
       </c>
       <c r="H1" s="6" t="inlineStr">
         <is>
-          <t>minPlayers</t>
+          <t>matchSeconds</t>
         </is>
       </c>
       <c r="I1" s="6" t="inlineStr">
         <is>
-          <t>matchSeconds</t>
+          <t>respawnSeconds</t>
         </is>
       </c>
       <c r="J1" s="6" t="inlineStr">
         <is>
-          <t>respawnSeconds</t>
+          <t>protectionSeconds</t>
         </is>
       </c>
       <c r="K1" s="6" t="inlineStr">
         <is>
-          <t>protectionSeconds</t>
+          <t>friendlyFire</t>
         </is>
       </c>
       <c r="L1" s="6" t="inlineStr">
-        <is>
-          <t>friendlyFire</t>
-        </is>
-      </c>
-      <c r="M1" s="6" t="inlineStr">
         <is>
           <t>groundOnlyScore</t>
         </is>
@@ -463,7 +458,7 @@
       </c>
       <c r="H2" s="6" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="I2" s="6" t="inlineStr">
@@ -478,15 +473,10 @@
       </c>
       <c r="K2" s="6" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="L2" s="6" t="inlineStr">
-        <is>
-          <t>bool</t>
-        </is>
-      </c>
-      <c r="M2" s="6" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
@@ -510,50 +500,45 @@
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>默认角色 ID</t>
+          <t>默认英雄 ID</t>
         </is>
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
-          <t>默认武器 ID</t>
+          <t>地图 ID</t>
         </is>
       </c>
       <c r="F3" s="9" t="inlineStr">
         <is>
-          <t>地图 ID</t>
+          <t>最大人数（当前场景上限 4）</t>
         </is>
       </c>
       <c r="G3" s="9" t="inlineStr">
         <is>
-          <t>最大人数（当前场景上限 4）</t>
+          <t>最低开局人数</t>
         </is>
       </c>
       <c r="H3" s="9" t="inlineStr">
         <is>
-          <t>最低开局人数</t>
+          <t>比赛时长（秒）</t>
         </is>
       </c>
       <c r="I3" s="9" t="inlineStr">
         <is>
-          <t>比赛时长（秒）</t>
+          <t>重生等待（秒）</t>
         </is>
       </c>
       <c r="J3" s="9" t="inlineStr">
         <is>
-          <t>重生等待（秒）</t>
+          <t>重生保护（秒）</t>
         </is>
       </c>
       <c r="K3" s="9" t="inlineStr">
         <is>
-          <t>重生保护（秒）</t>
+          <t>是否友伤</t>
         </is>
       </c>
       <c r="L3" s="9" t="inlineStr">
-        <is>
-          <t>是否友伤</t>
-        </is>
-      </c>
-      <c r="M3" s="9" t="inlineStr">
         <is>
           <t>仅可行走地面计分（含坡道、高台及桥面）</t>
         </is>
@@ -576,27 +561,24 @@
         <v>1</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H4" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J4" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="I4" s="5" t="n">
-        <v>180</v>
-      </c>
-      <c r="J4" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="K4" s="5" t="n">
-        <v>2</v>
+      <c r="K4" s="5" t="b">
+        <v>0</v>
       </c>
       <c r="L4" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5" t="b">
         <v>1</v>
       </c>
     </row>

--- a/Config/Luban/source/TbRoomMode.xlsx
+++ b/Config/Luban/source/TbRoomMode.xlsx
@@ -340,7 +340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="1" min="1" max="1"/>
@@ -355,7 +355,6 @@
     <col width="22" customWidth="1" style="1" min="10" max="10"/>
     <col width="22" customWidth="1" style="1" min="11" max="11"/>
     <col width="22" customWidth="1" style="1" min="12" max="12"/>
-    <col width="22" customWidth="1" style="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -414,11 +413,6 @@
           <t>friendlyFire</t>
         </is>
       </c>
-      <c r="L1" s="6" t="inlineStr">
-        <is>
-          <t>groundOnlyScore</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
@@ -476,11 +470,6 @@
           <t>bool</t>
         </is>
       </c>
-      <c r="L2" s="6" t="inlineStr">
-        <is>
-          <t>bool</t>
-        </is>
-      </c>
     </row>
     <row r="3" ht="42" customHeight="1" s="1">
       <c r="A3" s="9" t="inlineStr">
@@ -510,7 +499,7 @@
       </c>
       <c r="F3" s="9" t="inlineStr">
         <is>
-          <t>最大人数（当前场景上限 4）</t>
+          <t>最大人数（当前场景上限 8，每队最多 4 人）</t>
         </is>
       </c>
       <c r="G3" s="9" t="inlineStr">
@@ -536,11 +525,6 @@
       <c r="K3" s="9" t="inlineStr">
         <is>
           <t>是否友伤</t>
-        </is>
-      </c>
-      <c r="L3" s="9" t="inlineStr">
-        <is>
-          <t>仅可行走地面计分（含坡道、高台及桥面）</t>
         </is>
       </c>
     </row>
@@ -561,7 +545,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G4" s="5" t="n">
         <v>2</v>
@@ -577,9 +561,6 @@
       </c>
       <c r="K4" s="5" t="b">
         <v>0</v>
-      </c>
-      <c r="L4" s="5" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Luban/source/TbRoomMode.xlsx
+++ b/Config/Luban/source/TbRoomMode.xlsx
@@ -340,7 +340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="1" min="1" max="1"/>
@@ -354,7 +354,14 @@
     <col width="22" customWidth="1" style="1" min="9" max="9"/>
     <col width="22" customWidth="1" style="1" min="10" max="10"/>
     <col width="22" customWidth="1" style="1" min="11" max="11"/>
-    <col width="22" customWidth="1" style="1" min="12" max="12"/>
+    <col width="30" customWidth="1" style="1" min="12" max="12"/>
+    <col width="30" customWidth="1" style="1" min="13" max="13"/>
+    <col width="30" customWidth="1" style="1" min="14" max="14"/>
+    <col width="30" customWidth="1" style="1" min="15" max="15"/>
+    <col width="30" customWidth="1" style="1" min="16" max="16"/>
+    <col width="30" customWidth="1" style="1" min="17" max="17"/>
+    <col width="30" customWidth="1" style="1" min="18" max="18"/>
+    <col width="30" customWidth="1" style="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -413,6 +420,46 @@
           <t>friendlyFire</t>
         </is>
       </c>
+      <c r="L1" s="6" t="inlineStr">
+        <is>
+          <t>bubbleSeconds</t>
+        </is>
+      </c>
+      <c r="M1" s="6" t="inlineStr">
+        <is>
+          <t>bubbleMoveSpeed</t>
+        </is>
+      </c>
+      <c r="N1" s="6" t="inlineStr">
+        <is>
+          <t>bubbleGravity</t>
+        </is>
+      </c>
+      <c r="O1" s="6" t="inlineStr">
+        <is>
+          <t>bubbleFallSpeed</t>
+        </is>
+      </c>
+      <c r="P1" s="6" t="inlineStr">
+        <is>
+          <t>bubbleBounceSpeed</t>
+        </is>
+      </c>
+      <c r="Q1" s="6" t="inlineStr">
+        <is>
+          <t>bubbleInteractionRange</t>
+        </is>
+      </c>
+      <c r="R1" s="6" t="inlineStr">
+        <is>
+          <t>bubblePaintRadius</t>
+        </is>
+      </c>
+      <c r="S1" s="6" t="inlineStr">
+        <is>
+          <t>bubblePadding</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
@@ -470,6 +517,46 @@
           <t>bool</t>
         </is>
       </c>
+      <c r="L2" s="6" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="M2" s="6" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N2" s="6" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="O2" s="6" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="S2" s="6" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="42" customHeight="1" s="1">
       <c r="A3" s="9" t="inlineStr">
@@ -525,6 +612,46 @@
       <c r="K3" s="9" t="inlineStr">
         <is>
           <t>是否友伤</t>
+        </is>
+      </c>
+      <c r="L3" s="9" t="inlineStr">
+        <is>
+          <t>待救泡泡时长（秒）</t>
+        </is>
+      </c>
+      <c r="M3" s="9" t="inlineStr">
+        <is>
+          <t>泡泡水平速度（米/秒）</t>
+        </is>
+      </c>
+      <c r="N3" s="9" t="inlineStr">
+        <is>
+          <t>泡泡重力（米/秒²）</t>
+        </is>
+      </c>
+      <c r="O3" s="9" t="inlineStr">
+        <is>
+          <t>泡泡最大下落速度（米/秒）</t>
+        </is>
+      </c>
+      <c r="P3" s="9" t="inlineStr">
+        <is>
+          <t>泡泡反弹速度（米/秒）</t>
+        </is>
+      </c>
+      <c r="Q3" s="9" t="inlineStr">
+        <is>
+          <t>距泡泡表面的交互距离（米）</t>
+        </is>
+      </c>
+      <c r="R3" s="9" t="inlineStr">
+        <is>
+          <t>死亡泡泡涂墨半径（米）</t>
+        </is>
+      </c>
+      <c r="S3" s="9" t="inlineStr">
+        <is>
+          <t>泡泡包裹人物的余量（米）</t>
         </is>
       </c>
     </row>
@@ -562,6 +689,30 @@
       <c r="K4" s="5" t="b">
         <v>0</v>
       </c>
+      <c r="L4" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="O4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R4" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="S4" s="5" t="n">
+        <v>0.2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/Luban/source/TbRoomMode.xlsx
+++ b/Config/Luban/source/TbRoomMode.xlsx
@@ -662,7 +662,7 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>三分钟涂地赛</t>
+          <t>三分钟积木赛</t>
         </is>
       </c>
       <c r="D4" s="5" t="n">
